--- a/public/CuentasCuentas/deudores-anticipos-comprobación-CuentasSeguidas.xlsx
+++ b/public/CuentasCuentas/deudores-anticipos-comprobación-CuentasSeguidas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dmijangos\Documents\SAC-IPE\public\CuentasCuentas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F16D21-9F36-48FC-BA48-A4D605A9925D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44039952-7691-4EA1-98DD-1C0CDAC348B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA794CD9-A794-4D6D-97A5-04484BD59B08}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15492" uniqueCount="1253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15512" uniqueCount="1258">
   <si>
     <t>cuenta</t>
   </si>
@@ -3795,6 +3795,21 @@
   </si>
   <si>
     <t>5.1.3.9.09.02</t>
+  </si>
+  <si>
+    <t>1.1.1.2.02.01</t>
+  </si>
+  <si>
+    <t>2.1.1.7.01.03</t>
+  </si>
+  <si>
+    <t>2.1.1.7.01.04</t>
+  </si>
+  <si>
+    <t>2.1.1.7.01.05</t>
+  </si>
+  <si>
+    <t>2.1.1.7.01.07</t>
   </si>
 </sst>
 </file>
@@ -58403,24 +58418,74 @@
       </c>
     </row>
     <row r="3874" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B3874" s="2"/>
-      <c r="C3874" s="2"/>
+      <c r="A3874" s="3" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B3874" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3874" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3874" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3875" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B3875" s="2"/>
-      <c r="C3875" s="2"/>
+      <c r="A3875" s="5" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B3875" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3875" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3875" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3876" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B3876" s="2"/>
-      <c r="C3876" s="2"/>
+      <c r="A3876" s="4" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B3876" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3876" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3876" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3877" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B3877" s="2"/>
-      <c r="C3877" s="2"/>
+      <c r="A3877" s="4" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B3877" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3877" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3877" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3878" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B3878" s="2"/>
-      <c r="C3878" s="2"/>
+      <c r="A3878" s="4" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B3878" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3878" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3878" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3879" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B3879" s="2"/>
